--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,26 +459,31 @@
           <t>O_FACILITY</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VASN1307DEV8880</t>
+          <t>VASN1407QA8110</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG13072025DEV86910000</t>
+          <t>0000VG14072025QA63020000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>203040-001-MISC</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -487,28 +492,33 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VASN1307DEV8880</t>
+          <t>VASN1407QA8110</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG13072025DEV19910001</t>
+          <t>0000VG14072025QA13520001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>203040-001-MISC</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -517,6 +527,501 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VASN1407QA8110</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA64410002</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VASN1407QA8110</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA82420003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VASN1407QA8110</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA76320004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VASN1407QA8110</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA11480005</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VASN1407QA8390</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA74290006</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VASN1407QA8390</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA67090007</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VASN1407QA8390</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA33050008</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VASN1407QA8390</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA33260009</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VASN1407QA1170</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA15110010</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VASN1407QA1170</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA99930011</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VASN1407QA3030</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA58620012</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VASN1407QA3030</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA98240013</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VASN1407QA7150</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA23570014</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VASN1407QA7150</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0000VG14072025QA98290015</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AUPU</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VASN1407QA8110</t>
+          <t>VASN1407QA3950</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG14072025QA63020000</t>
+          <t>0000VG14072025QA56700000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -508,17 +508,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VASN1407QA8110</t>
+          <t>VASN1407QA3950</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG14072025QA13520001</t>
+          <t>0000VG14072025QA49840001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -530,496 +530,6 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VASN1407QA8110</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA64410002</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>420420-420-M</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>VASN1407QA8110</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA82420003</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>420420-420-M</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>VASN1407QA8110</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA76320004</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>VASN1407QA8110</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA11480005</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>VASN1407QA8390</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA74290006</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VASN1407QA8390</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA67090007</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VASN1407QA8390</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA33050008</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VASN1407QA8390</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA33260009</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>VASN1407QA1170</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA15110010</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>VASN1407QA1170</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA99930011</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>VASN1407QA3030</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA58620012</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>VASN1407QA3030</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA98240013</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>VASN1407QA7150</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA23570014</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>420420-420-M</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>VASN1407QA7150</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0000VG14072025QA98290015</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>420420-420-M</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VASN1407QA3950</t>
+          <t>VASN1607QA2060</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG14072025QA56700000</t>
+          <t>0000VG16072025QA71880000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>420420-420-M</t>
+          <t>AC4081-014-MISC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -508,17 +508,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VASN1407QA3950</t>
+          <t>VASN1607QA2060</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG14072025QA49840001</t>
+          <t>0000VG16072025QA89280001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>420420-420-M</t>
+          <t>AC4081-014-MISC</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VASN1607QA2060</t>
+          <t>VASN1707QA9600</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG16072025QA71880000</t>
+          <t>0000VG17072025QA92000000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AC4081-014-MISC</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -508,17 +508,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VASN1607QA2060</t>
+          <t>VASN1707QA5570</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG16072025QA89280001</t>
+          <t>0000VG17072025QA90870001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AC4081-014-MISC</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -530,6 +530,41 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VASN1707QA5570</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA68860002</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,21 +473,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VASN1707QA9600</t>
+          <t>VASN1707QA6000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG17072025QA92000000</t>
+          <t>0000VG17072025QA44650000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DC2380-447-4</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,12 +508,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VASN1707QA5570</t>
+          <t>VASN1707QA6000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG17072025QA90870001</t>
+          <t>0000VG17072025QA89770001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,21 +543,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VASN1707QA5570</t>
+          <t>VASN1707QA6000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0000VG17072025QA68860002</t>
+          <t>0000VG17072025QA50640002</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -565,6 +565,1301 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA40270003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA65550004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA57090005</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA57330006</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA28710007</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA44150008</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA72830009</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA77570010</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA82980011</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA53950012</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA17500013</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA35980014</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA92230015</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA99680016</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA63740017</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA47150018</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VASN1707QA6000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA90470019</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA25240020</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA76280021</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA55870022</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA36800023</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA36400024</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA13930025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA73730026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA10970027</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA98400028</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA27370029</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA60440030</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA61890031</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA83660032</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA20240033</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA27710034</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA27260035</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA70400036</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA59650037</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA68780038</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>VASN1707QA4701</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA60050039</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DN0560-885-6</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,21 +473,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG17072025QA44650000</t>
+          <t>0000VG18072025QA42130000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,21 +508,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG17072025QA89770001</t>
+          <t>0000VG18072025QA35500001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,21 +543,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0000VG17072025QA50640002</t>
+          <t>0000VG18072025QA40570002</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -578,21 +578,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0000VG17072025QA40270003</t>
+          <t>0000VG18072025QA28270003</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -613,21 +613,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0000VG17072025QA65550004</t>
+          <t>0000VG18072025QA34600004</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -648,21 +648,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0000VG17072025QA57090005</t>
+          <t>0000VG18072025QA87350005</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -683,21 +683,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0000VG17072025QA57330006</t>
+          <t>0000VG18072025QA61330006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -718,21 +718,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0000VG17072025QA28710007</t>
+          <t>0000VG18072025QA68470007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -753,21 +753,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0000VG17072025QA44150008</t>
+          <t>0000VG18072025QA86370008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9170</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0000VG17072025QA72830009</t>
+          <t>0000VG18072025QA31700009</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -823,21 +823,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0000VG17072025QA77570010</t>
+          <t>0000VG18072025QA37120010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -858,21 +858,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0000VG17072025QA82980011</t>
+          <t>0000VG18072025QA22000011</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -893,21 +893,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0000VG17072025QA53950012</t>
+          <t>0000VG18072025QA27840012</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0000VG17072025QA17500013</t>
+          <t>0000VG18072025QA84210013</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -963,21 +963,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0000VG17072025QA35980014</t>
+          <t>0000VG18072025QA90820014</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -998,21 +998,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0000VG17072025QA92230015</t>
+          <t>0000VG18072025QA69740015</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0000VG17072025QA99680016</t>
+          <t>0000VG18072025QA31430016</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1068,21 +1068,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0000VG17072025QA63740017</t>
+          <t>0000VG18072025QA39040017</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0000VG17072025QA47150018</t>
+          <t>0000VG18072025QA58190018</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VASN1707QA6000</t>
+          <t>JVASN1807QA9611</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0000VG17072025QA90470019</t>
+          <t>0000VG18072025QA75820019</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DN0560-885-6</t>
+          <t>DC2380-447-4</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1160,706 +1160,6 @@
         </is>
       </c>
       <c r="G21" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA25240020</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA76280021</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA55870022</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA36800023</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA36400024</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA13930025</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA73730026</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA10970027</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA98400028</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA27370029</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA60440030</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA61890031</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>10</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA83660032</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>10</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA20240033</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>10</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA27710034</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>10</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA27260035</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA70400036</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>10</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA59650037</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>10</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA68780038</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>10</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>VASN1707QA4701</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0000VG17072025QA60050039</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DN0560-885-6</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,12 +473,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JVASN1807QA9170</t>
+          <t>VGASN2107QA6640</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG18072025QA42130000</t>
+          <t>0000VG21072025QA86650000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,12 +508,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JVASN1807QA9170</t>
+          <t>VGASN2107QA6640</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG18072025QA35500001</t>
+          <t>0000VG21072025QA25890001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JVASN1807QA9170</t>
+          <t>VGASN2107QA4391</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0000VG18072025QA40570002</t>
+          <t>0000VG21072025QA65710002</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JVASN1807QA9170</t>
+          <t>VGASN2107QA4391</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0000VG18072025QA28270003</t>
+          <t>0000VG21072025QA54300003</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,566 +600,6 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9170</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA34600004</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9170</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA87350005</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9170</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA61330006</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9170</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA68470007</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9170</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA86370008</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9170</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA31700009</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA37120010</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA22000011</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA27840012</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA84210013</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA90820014</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA69740015</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA31430016</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA39040017</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA58190018</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>JVASN1807QA9611</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0000VG18072025QA75820019</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VGASN2107QA6640</t>
+          <t>VGASN2107QA9450</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG21072025QA86650000</t>
+          <t>0000VG07212025QA51680000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DC2380-447-4</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -508,17 +508,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VGASN2107QA6640</t>
+          <t>VGASN2107QA9450</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG21072025QA25890001</t>
+          <t>0000VG07212025QA81720001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DC2380-447-4</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -530,76 +530,6 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VGASN2107QA4391</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0000VG21072025QA65710002</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>VGASN2107QA4391</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0000VG21072025QA54300003</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DC2380-447-4</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,12 +473,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VGASN2107QA9450</t>
+          <t>VGASN0722QA6520</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG07212025QA51680000</t>
+          <t>0000VG07222025QA43750000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,12 +508,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VGASN2107QA9450</t>
+          <t>VGASN0722QA6520</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG07212025QA81720001</t>
+          <t>0000VG07222025QA14210001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,6 +530,76 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VGASN0722QA4571</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0000VG07222025QA49200002</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VGASN0722QA4571</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0000VG07222025QA20210003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VGASN0722QA6520</t>
+          <t>VGASN0723QA1350</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0000VG07222025QA43750000</t>
+          <t>00V07232025QA6600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,12 +508,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VGASN0722QA6520</t>
+          <t>VGASN0723QA1350</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0000VG07222025QA14210001</t>
+          <t>00V07232025QA1121</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VGASN0722QA4571</t>
+          <t>VGASN0723QA6411</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0000VG07222025QA49200002</t>
+          <t>00V07232025QA2122</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VGASN0722QA4571</t>
+          <t>VGASN0723QA6411</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0000VG07222025QA20210003</t>
+          <t>00V07232025QA5173</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,76 +425,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>PLANT</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>ENVN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ASN_ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LPN_ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ITEM_ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>O_FACILITY</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Carrier</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>VGASN0723QA1350</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00V07232025QA6600</t>
+          <t>VGASN0724QA7140</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>00V07242025QA2830</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>DD9293-100-7</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0005005401</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>
@@ -503,33 +513,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>VGASN0723QA1350</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>00V07232025QA1121</t>
+          <t>VGASN0724QA7140</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>00V07242025QA9201</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>DD9293-100-7</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0005005401</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>
@@ -538,33 +553,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VGASN0723QA6411</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>00V07232025QA2122</t>
+          <t>VGASN0724QA9131</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>00V07242025QA7252</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>DD9293-100-7</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>6</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0005005401</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>
@@ -573,33 +593,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>VGASN0723QA6411</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>00V07232025QA5173</t>
+          <t>VGASN0724QA9131</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>00V07242025QA5793</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>DD9293-100-7</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>6</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0005005401</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140</t>
+          <t>VGASN0725QA7080</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA2830</t>
+          <t>00V07252025QA5420</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140</t>
+          <t>VGASN0725QA7080</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V07242025QA9201</t>
+          <t>00V07252025QA5681</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0724QA9131</t>
+          <t>VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V07242025QA7252</t>
+          <t>00V07252025QA8922</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN0724QA9131</t>
+          <t>VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00V07242025QA5793</t>
+          <t>00V07252025QA2143</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080</t>
+          <t>VGASN0725QA7840</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA5420</t>
+          <t>00V07252025QA6990</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080</t>
+          <t>VGASN0725QA7840</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V07252025QA5681</t>
+          <t>00V07252025QA2271</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0725QA9771</t>
+          <t>VGASN0725QA7840</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V07252025QA8922</t>
+          <t>00V07252025QA1452</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -603,17 +603,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN0725QA9771</t>
+          <t>VGASN0725QA7840</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00V07252025QA2143</t>
+          <t>00V07252025QA9213</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -625,6 +625,206 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN0725QA7840</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V07252025QA7424</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN0725QA7840</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V07252025QA1235</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN0725QA9531</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V07252025QA2916</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN0725QA9531</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V07252025QA3647</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN0725QA9531</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00V07252025QA7468</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840</t>
+          <t>VGASN0725QA9930</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA6990</t>
+          <t>00V07252025QA8610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840</t>
+          <t>VGASN0725QA9930</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V07252025QA2271</t>
+          <t>00V07252025QA2461</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840</t>
+          <t>VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V07252025QA1452</t>
+          <t>00V07252025QA5842</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>420420-420-M</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -603,17 +603,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840</t>
+          <t>VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00V07252025QA9213</t>
+          <t>00V07252025QA4313</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>420420-420-M</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -625,206 +625,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN0725QA7840</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V07252025QA7424</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN0725QA7840</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V07252025QA1235</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN0725QA9531</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00V07252025QA2916</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN0725QA9531</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00V07252025QA3647</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>420420-420-M</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>VGASN0725QA9531</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>00V07252025QA7468</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA9930</t>
+          <t>VGASN0729QA2750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA8610</t>
+          <t>00V07292025QA3880</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,126 +505,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN0725QA9930</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V07252025QA2461</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN0725QA8371</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V07252025QA5842</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN0725QA8371</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V07252025QA4313</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2750</t>
+          <t>VGASN0729QA6420</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3880</t>
+          <t>00V07292025QA2670</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -505,6 +505,286 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN0729QA6420</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V07292025QA1311</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN0729QA6420</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V07292025QA6122</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0729QA6420</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V07292025QA7733</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN0729QA2901</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V07292025QA8724</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN0729QA2901</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V07292025QA2235</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN0729QA2901</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V07292025QA2736</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN0729QA2901</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V07292025QA1897</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA2670</t>
+          <t>00V07312025QA6360</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>112308-011-XL</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V07292025QA1311</t>
+          <t>00V07312025QA7221</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>112308-011-XL</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,246 +545,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN0729QA6420</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V07292025QA6122</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN0729QA6420</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V07292025QA7733</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN0729QA2901</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V07292025QA8724</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN0729QA2901</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V07292025QA2235</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN0729QA2901</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00V07292025QA2736</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN0729QA2901</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00V07292025QA1897</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA6360</t>
+          <t>00V07312025QA2460</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V07312025QA7221</t>
+          <t>00V07312025QA6401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA2460</t>
+          <t>00V08032025QA7350</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>112308-011-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V07312025QA6401</t>
+          <t>00V08032025QA5991</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>112308-011-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,6 +545,86 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>81ASN0803QA2340</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V08032025QA2232</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>81ASN0803QA2340</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V08032025QA6313</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0803QA2340</t>
+          <t>VGASN0805QA5760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08032025QA7350</t>
+          <t>00V08052025QA6610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,126 +505,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>81ASN0803QA2340</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V08032025QA5991</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>81ASN0803QA2340</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V08032025QA2232</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>81ASN0803QA2340</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V08032025QA6313</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA2970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA2770</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0806QA2970</t>
+          <t>VGASN0806QA2840</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08062025QA2770</t>
+          <t>00V08062025QA4760</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,6 +505,126 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN0806QA2840</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V08062025QA3231</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN0806QA2840</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V08062025QA1932</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0806QA2840</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V08062025QA3253</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0806QA2840</t>
+          <t>VGASN0806QA3170</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08062025QA4760</t>
+          <t>00V08062025QA4010</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,126 +505,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN0806QA2840</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V08062025QA3231</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN0806QA2840</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V08062025QA1932</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN0806QA2840</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V08062025QA3253</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0806QA3170</t>
+          <t>VGASN0806QA5260</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08062025QA4010</t>
+          <t>00V08062025QA3890</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0806QA5260</t>
+          <t>VGASN0807QA6190</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08062025QA3890</t>
+          <t>00V08072025QA6520</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,6 +505,126 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN0807QA6190</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V08072025QA5691</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN0807QA6190</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V08072025QA8392</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0807QA6190</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V08072025QA5833</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0807QA6190</t>
+          <t>VGASN0807QA6470</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08072025QA6520</t>
+          <t>00V08072025QA8540</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0807QA6190</t>
+          <t>VGASN0807QA6470</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V08072025QA5691</t>
+          <t>00V08072025QA3031</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0807QA6190</t>
+          <t>VGASN0807QA6470</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V08072025QA8392</t>
+          <t>00V08072025QA8512</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN0807QA6190</t>
+          <t>VGASN0807QA6470</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00V08072025QA5833</t>
+          <t>00V08072025QA7163</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0807QA6470</t>
+          <t>VGASN0807QA9430</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08072025QA8540</t>
+          <t>00V08072025QA8490</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0807QA6470</t>
+          <t>VGASN0807QA9430</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V08072025QA3031</t>
+          <t>00V08072025QA1571</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -545,86 +545,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN0807QA6470</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V08072025QA8512</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN0807QA6470</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V08072025QA7163</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>924156-100-S</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0807QA9430</t>
+          <t>VGASN0821QA4940</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08072025QA8490</t>
+          <t>00V08212025QA6060</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>924156-365-M</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0807QA9430</t>
+          <t>VGASN0821QA4940</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V08072025QA1571</t>
+          <t>00V08212025QA9731</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>924156-365-M</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,6 +545,406 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4940</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V08212025QA1212</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>924157-417-2XL</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4940</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V08212025QA2993</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>924157-417-2XL</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4940</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V08212025QA6144</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>924156-836-XL</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4940</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V08212025QA6275</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>924156-836-XL</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4851</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V08212025QA6066</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>924156-365-M</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4851</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V08212025QA6877</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>924156-365-M</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4851</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00V08212025QA6078</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>924157-417-2XL</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4851</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00V08212025QA3019</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>924157-417-2XL</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4851</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00V08212025QA31110</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>924156-836-XL</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VGASN0821QA4851</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00V08212025QA27511</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>924156-836-XL</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0821QA4940</t>
+          <t>VGASN0822QA3290</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08212025QA6060</t>
+          <t>00V08222025QA27300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0821QA4940</t>
+          <t>VGASN0822QA3290</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V08212025QA9731</t>
+          <t>00V08222025QA17401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-365-M</t>
+          <t>924157-417-2XL</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0821QA4940</t>
+          <t>VGASN0822QA3290</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V08212025QA1212</t>
+          <t>00V08222025QA54002</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>924157-417-2XL</t>
+          <t>924156-836-XL</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -585,366 +585,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4940</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V08212025QA2993</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>924157-417-2XL</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4940</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V08212025QA6144</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>924156-836-XL</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4940</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V08212025QA6275</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>924156-836-XL</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4851</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00V08212025QA6066</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>924156-365-M</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4851</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00V08212025QA6877</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>924156-365-M</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4851</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>00V08212025QA6078</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>924157-417-2XL</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4851</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>00V08212025QA3019</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>924157-417-2XL</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4851</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>00V08212025QA31110</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>924156-836-XL</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>VGASN0821QA4851</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>00V08212025QA27511</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>924156-836-XL</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0822QA3290</t>
+          <t>VGASN0824QA1320</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08222025QA27300</t>
+          <t>00V08242025QA14900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-365-M</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -505,86 +505,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN0822QA3290</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V08222025QA17401</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>924157-417-2XL</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN0822QA3290</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V08222025QA54002</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>924156-836-XL</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0824QA1320</t>
+          <t>VGASN0825QA8410</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08242025QA14900</t>
+          <t>00V08252025QA11000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>924156-365-S</t>
         </is>
       </c>
       <c r="F2" t="n">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0825QA8410</t>
+          <t>VGASN0902QA9940</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08252025QA11000</t>
+          <t>00V09022025QA65200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-365-S</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -505,6 +505,46 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN0902QA9940</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V09022025QA95101</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0902QA9940</t>
+          <t>VGASN0903QA4760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09022025QA65200</t>
+          <t>00V09032025QA25700</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>924156-365-L</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0902QA9940</t>
+          <t>VGASN0903QA4760</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V09022025QA95101</t>
+          <t>00V09032025QA28501</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>924156-365-L</t>
         </is>
       </c>
       <c r="F3" t="n">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0903QA4760</t>
+          <t>VGASN0904QA1420</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09032025QA25700</t>
+          <t>00V09042025QA58900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0903QA4760</t>
+          <t>VGASN0904QA1420</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V09032025QA28501</t>
+          <t>00V09042025QA36801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,21 +483,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0904QA1420</t>
+          <t>VGASN0910QA2140</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09042025QA58900</t>
+          <t>00V09102025QA94800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-365-L</t>
+          <t>829748-010-S</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -523,21 +523,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0904QA1420</t>
+          <t>VGASN0910QA2140</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V09042025QA36801</t>
+          <t>00V09102025QA64501</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-365-L</t>
+          <t>829748-010-S</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -545,6 +545,126 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN0910QA2140</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V09102025QA65302</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>829748-010-S</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0910QA2140</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V09102025QA47503</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>829747-091-XL</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN0910QA2140</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V09102025QA39304</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>829747-091-XL</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0910QA2140</t>
+          <t>VGASN0911QA1480</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09102025QA94800</t>
+          <t>00V09112025QA66900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>829748-010-S</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0910QA2140</t>
+          <t>VGASN0911QA1480</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V09102025QA64501</t>
+          <t>00V09112025QA73801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>829748-010-S</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0910QA2140</t>
+          <t>VGASN0911QA1480</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V09102025QA65302</t>
+          <t>00V09112025QA22302</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>829748-010-S</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -585,86 +585,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN0910QA2140</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V09102025QA47503</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>829747-091-XL</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN0910QA2140</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V09102025QA39304</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>829747-091-XL</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,21 +483,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0911QA1480</t>
+          <t>VGASN0918QA4990</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09112025QA66900</t>
+          <t>00V09182025QA24600</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>123456-001-TST</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -523,21 +523,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0911QA1480</t>
+          <t>VGASN0918QA4990</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V09112025QA73801</t>
+          <t>00V09182025QA76801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>123456-001-TST</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -563,21 +563,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0911QA1480</t>
+          <t>VGASN0918QA4990</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V09112025QA22302</t>
+          <t>00V09182025QA39602</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>123456-001-TST</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -585,6 +585,686 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V09182025QA96803</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V09182025QA81504</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V09182025QA83905</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V09182025QA81206</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V09182025QA41207</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00V09182025QA97808</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00V09182025QA60209</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00V09182025QA89110</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00V09182025QA36311</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00V09182025QA85312</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00V09182025QA83913</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00V09182025QA95514</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00V09182025QA23215</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00V09182025QA52316</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00V09182025QA97717</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00V09182025QA39618</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VGASN0918QA4990</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00V09182025QA93619</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0926QA5640</t>
+          <t>VGASN0927QA8950</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09262025QA2483400</t>
+          <t>00V09272025QA7399900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>829748-010-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0926QA5640</t>
+          <t>VGASN0927QA8950</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V09262025QA2638401</t>
+          <t>00V09272025QA3214201</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>829748-010-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,6 +545,206 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN0927QA8950</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V09272025QA4053502</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN0927QA8950</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V09272025QA3621103</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN0927QA8950</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V09272025QA9923004</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN0927QA8950</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V09272025QA8941505</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN0927QA8950</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V09272025QA9193706</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0927QA8950</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V09272025QA7399900</t>
+          <t>00V10012025QA1736600</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN0927QA8950</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V09272025QA3214201</t>
+          <t>00V10012025QA7372301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN0927QA8950</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00V09272025QA4053502</t>
+          <t>00V10012025QA9183902</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -603,17 +603,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN0927QA8950</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00V09272025QA3621103</t>
+          <t>00V10012025QA6786203</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -643,17 +643,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VGASN0927QA8950</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00V09272025QA9923004</t>
+          <t>00V10012025QA7313704</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -683,17 +683,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VGASN0927QA8950</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00V09272025QA8941505</t>
+          <t>00V10012025QA4796105</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -723,17 +723,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VGASN0927QA8950</t>
+          <t>VGASN1001QA1100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00V09272025QA9193706</t>
+          <t>00V10012025QA4537706</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -745,6 +745,46 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN1001QA1100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V10012025QA2830407</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>829747-091-3XL</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1001QA1100</t>
+          <t>VGASN1008QA4550</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10012025QA1736600</t>
+          <t>00V10082025QA7782000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>829747-091-3XL</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1001QA1100</t>
+          <t>VGASN1008QA4550</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V10012025QA7372301</t>
+          <t>00V10082025QA6837501</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>829747-091-3XL</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,246 +545,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V10012025QA9183902</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V10012025QA6786203</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V10012025QA7313704</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V10012025QA4796105</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00V10012025QA4537706</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN1001QA1100</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00V10012025QA2830407</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>829747-091-3XL</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1008QA4550</t>
+          <t>VGASN1010QA1810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10082025QA7782000</t>
+          <t>00V10102025QA4058600</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1008QA4550</t>
+          <t>VGASN1010QA1810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V10082025QA6837501</t>
+          <t>00V10102025QA2050401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="F3" t="n">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1010QA1810</t>
+          <t>VGASN1013QA9900</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10102025QA4058600</t>
+          <t>00V10132025QA3984800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,46 +505,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1010QA1810</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V10102025QA2050401</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>DD9293-100-11.5</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,21 +483,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1013QA9900</t>
+          <t>VGASN1014QA9020</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10132025QA3984800</t>
+          <t>00V10142025QA8107600</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>303070-001-MISC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -505,6 +505,46 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1014QA9020</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V10142025QA7725701</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>303070-001-MISC</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,21 +483,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1014QA9020</t>
+          <t>VGASN1023QA3490</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10142025QA8107600</t>
+          <t>00V10232025QA5520800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>303070-001-MISC</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -505,46 +505,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1014QA9020</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V10142025QA7725701</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>303070-001-MISC</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1023QA3490</t>
+          <t>VGASN1025QA1710</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10232025QA5520800</t>
+          <t>00V10252025QA5767100</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,6 +505,86 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1025QA1710</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V10252025QA3139301</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1025QA3651</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V10252025QA8991102</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1025QA1710</t>
+          <t>VGASN1104QA1040</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10252025QA5767100</t>
+          <t>00V11042025QA1783600</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>136027-115-9.5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1025QA1710</t>
+          <t>VGASN1104QA1040</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V10252025QA3139301</t>
+          <t>00V11042025QA6105801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>136027-115-9.5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,46 +545,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1025QA3651</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V10252025QA8991102</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1104QA1040</t>
+          <t>VGASN1107QA2830</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11042025QA1783600</t>
+          <t>00V11072025QA6969400</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1104QA1040</t>
+          <t>VGASN1107QA2830</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11042025QA6105801</t>
+          <t>00V11072025QA8085801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -545,6 +545,286 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11072025QA6618802</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V11072025QA3998003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V11072025QA5036804</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>136027-115-9.5</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V11072025QA1481505</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00V11072025QA7682306</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00V11072025QA7690607</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VGASN1107QA2830</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00V11072025QA1452008</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>829747-091-S-T</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1107QA2830</t>
+          <t>VGASN1113QA7310</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11072025QA6969400</t>
+          <t>00V11132025QA5308300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>136027-115-9.5</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1107QA2830</t>
+          <t>VGASN1113QA7310</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11072025QA8085801</t>
+          <t>00V11132025QA8216301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>136027-115-9.5</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,286 +545,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V11072025QA6618802</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V11072025QA3998003</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V11072025QA5036804</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>136027-115-9.5</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V11072025QA1481505</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>829747-091-S-T</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00V11072025QA7682306</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>829747-091-S-T</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00V11072025QA7690607</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>829747-091-S-T</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>VGASN1107QA2830</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>00V11072025QA1452008</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>829747-091-S-T</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1113QA7310</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11132025QA5308300</t>
+          <t>00V11252025QA8409300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1113QA7310</t>
+          <t>VGASN1125QA4410</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11132025QA8216301</t>
+          <t>00V11252025QA9579401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="F3" t="n">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11252025QA8409300</t>
+          <t>00V11262025QA3029500</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1125QA4410</t>
+          <t>VGASN1126QA8010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11252025QA9579401</t>
+          <t>00V11262025QA2169401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1126QA8010</t>
+          <t>VGASN1202QA7980</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11262025QA3029500</t>
+          <t>00V12022025QA5770600</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>FN2329-010-XL</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1126QA8010</t>
+          <t>VGASN1202QA7980</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V11262025QA2169401</t>
+          <t>00V12022025QA1424501</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>FN2329-010-XL</t>
         </is>
       </c>
       <c r="F3" t="n">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1202QA7980</t>
+          <t>VGASN1203QA1590</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12022025QA5770600</t>
+          <t>00V12032025QA1811200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FN2329-010-XL</t>
+          <t>927205-043-S</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -505,46 +505,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1202QA7980</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V12022025QA1424501</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FN2329-010-XL</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>VGASN1204QA3110</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>00V12042025QA3274100</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1204QA3110</t>
+          <t>81ASN1210QA4500</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12042025QA3274100</t>
+          <t>00081121020256691800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>432997-128-10</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -505,6 +505,46 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>81ASN1210QA4500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00081121020256872801</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>432997-128-10</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN1210QA4500</t>
+          <t>VGASN1212QA2740</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081121020256691800</t>
+          <t>00081121220258992000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>432997-128-10</t>
+          <t>AJ7566-010-LT</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN1210QA4500</t>
+          <t>VGASN1212QA2740</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081121020256872801</t>
+          <t>00081121220252585001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>432997-128-10</t>
+          <t>AJ7566-010-LT</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -545,6 +545,166 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1212QA2740</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00081121220257518502</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AJ7566-010-LT</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1212QA2740</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00081121220257940003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AJ7566-010-LT</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1212QA2740</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00081121220259291104</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AJ7566-010-LT</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1212QA2740</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081121220257403305</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AJ7566-010-LT</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1212QA2740</t>
+          <t>81ASN1219QA1580</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081121220258992000</t>
+          <t>00081121920253492500</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AJ7566-010-LT</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1212QA2740</t>
+          <t>81ASN1219QA1580</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081121220252585001</t>
+          <t>00081121920255700701</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AJ7566-010-LT</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VGASN1212QA2740</t>
+          <t>81ASN1219QA1580</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081121220257518502</t>
+          <t>00081121920258346802</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AJ7566-010-LT</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -603,17 +603,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VGASN1212QA2740</t>
+          <t>81ASN1219QA1580</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081121220257940003</t>
+          <t>00081121920255802103</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AJ7566-010-LT</t>
+          <t>DH6619-010-1</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -643,17 +643,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VGASN1212QA2740</t>
+          <t>81ASN1219QA9491</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00081121220259291104</t>
+          <t>00081121920255149004</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AJ7566-010-LT</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -683,17 +683,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VGASN1212QA2740</t>
+          <t>81ASN1219QA9491</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00081121220257403305</t>
+          <t>00081121920257937905</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AJ7566-010-LT</t>
+          <t>DH6619-010-4-5.5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -705,6 +705,86 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>81ASN1219QA9491</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00081121920258260606</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>81ASN1219QA9491</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00081121920255540007</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN1219QA1580</t>
+          <t>81ASN0108QA2570</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081121920253492500</t>
+          <t>00081010820268962700</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DH6619-010-4-5.5</t>
+          <t>829747-091-CUST2</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN1219QA1580</t>
+          <t>81ASN0108QA2570</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081121920255700701</t>
+          <t>00081010820264612401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DH6619-010-4-5.5</t>
+          <t>829747-091-CUST2</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN1219QA1580</t>
+          <t>81ASN0108QA4961</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081121920258346802</t>
+          <t>00081010820267174802</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DH6619-010-1</t>
+          <t>829747-091-CUST2</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -585,206 +585,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>81ASN1219QA1580</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00081121920255802103</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>DH6619-010-1</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>81ASN1219QA9491</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00081121920255149004</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>DH6619-010-4-5.5</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>81ASN1219QA9491</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00081121920257937905</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>DH6619-010-4-5.5</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>81ASN1219QA9491</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00081121920258260606</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>DH6619-010-1</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>81ASN1219QA9491</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00081121920255540007</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>DH6619-010-1</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0108QA2570</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081010820268962700</t>
+          <t>00081011420265699200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>829747-091-CUST2</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0108QA2570</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081010820264612401</t>
+          <t>00081011420269260301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>829747-091-CUST2</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN0108QA4961</t>
+          <t>81ASN0114QA1240</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081010820267174802</t>
+          <t>00081011420262662502</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>829747-091-CUST2</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -585,6 +585,166 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>81ASN0114QA1240</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00081011420267069203</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>81ASN0114QA6281</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00081011420262679904</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>81ASN0114QA6281</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081011420262595105</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>81ASN0114QA6281</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00081011420263133706</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DD9293-100-11.5</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081011420265699200</t>
+          <t>00081012220265611400</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081011420269260301</t>
+          <t>00081012220261758801</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,17 +563,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081011420262662502</t>
+          <t>00081012220261846502</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -603,17 +603,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>81ASN0114QA1240</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081011420267069203</t>
+          <t>00081012220262826603</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -643,17 +643,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>81ASN0114QA6281</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00081011420262679904</t>
+          <t>00081012220267077804</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -683,17 +683,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>81ASN0114QA6281</t>
+          <t>81ASN0122QA3510</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00081011420262595105</t>
+          <t>00081012220267664105</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -705,46 +705,6 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>81ASN0114QA6281</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>00081011420263133706</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>DD9293-100-11.5</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>81ASN0130QA9150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081012220265611400</t>
+          <t>00081013020264876100</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>81ASN0130QA9150</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081012220261758801</t>
+          <t>00081013020261202401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>81ASN0122QA3510</t>
+          <t>81ASN0130QA9150</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081012220261846502</t>
+          <t>00081013020265587102</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,126 +585,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00081012220262826603</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00081012220267077804</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>81ASN0122QA3510</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00081012220267664105</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>899371-091-M</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0508126100</t>
+          <t>0508293000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081081220260000001</t>
+          <t>00081082920260000007</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0508126100</t>
+          <t>0508293000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081081220260000002</t>
+          <t>00081082920260000008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
